--- a/data/trans_dic/P25C$otrosprofesionales_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 6,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,0; 5,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,3</t>
+          <t>0,88; 8,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,59</t>
+          <t>0,47; 4,48</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,07</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,94</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,32</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,3</t>
+          <t>0,62; 5,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,14</t>
+          <t>0,37; 3,19</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,41</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,16</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,1; 1,08</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,21</t>
+          <t>0,93; 3,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,4</t>
+          <t>0,4; 1,41</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía</t>
+          <t>Población cuyo método para dejar de fumar fue, al menos, acupuntura u homeparía (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1422</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 885</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1284</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1998</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4548</t>
+          <t>0; 4307</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5197</t>
+          <t>0; 4570</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1432</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3020</t>
+          <t>0; 3099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3133</t>
+          <t>0; 2604</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5518</t>
+          <t>0; 5086</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>514; 4249</t>
+          <t>513; 4672</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1027; 7012</t>
+          <t>719; 6835</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1045</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 753</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 941</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 1100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 997</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1092</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5257</t>
+          <t>0; 4368</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>579; 5030</t>
+          <t>586; 5516</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>826; 6807</t>
+          <t>800; 6915</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 8335</t>
+          <t>0; 8284</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2906</t>
+          <t>0; 3093</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8296</t>
+          <t>0; 8386</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>832; 9049</t>
+          <t>834; 9150</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3141; 10839</t>
+          <t>3137; 11316</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4438; 16629</t>
+          <t>4726; 16793</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$otrosprofesionales_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P25C$otrosprofesionales_2023-Provincia-trans_dic.xlsx
@@ -604,12 +604,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,58</t>
+          <t>0,0; 7,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,72</t>
         </is>
       </c>
     </row>
@@ -654,12 +654,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,38</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,03</t>
+          <t>0,83; 7,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,48</t>
+          <t>0,67; 4,89</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 4,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,82</t>
+          <t>0,66; 6,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,19</t>
+          <t>0,55; 3,36</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,57; 4,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,13</t>
+          <t>0,0; 5,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,43; 4,24</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,08</t>
+          <t>0,3; 1,54</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,35</t>
+          <t>1,07; 3,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,41</t>
+          <t>0,72; 1,9</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1448</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1457</t>
+          <t>1448</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4307</t>
+          <t>0; 5063</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4570</t>
+          <t>0; 5040</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>590</t>
         </is>
       </c>
     </row>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3099</t>
+          <t>0; 3225</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2604</t>
+          <t>0; 3166</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1195</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1702</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>3646</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>0; 7369</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>513; 4672</t>
+          <t>538; 4616</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>719; 6835</t>
+          <t>1162; 8441</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>971</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3709</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4368</t>
+          <t>0; 6297</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>586; 5516</t>
+          <t>708; 6487</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>800; 6915</t>
+          <t>1375; 8381</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>615</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2371</t>
+          <t>2623</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0; 8284</t>
+          <t>647; 5467</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>0; 2525</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 8386</t>
+          <t>683; 6689</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3893</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>7092</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>12016</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>834; 9150</t>
+          <t>2000; 10157</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3137; 11316</t>
+          <t>3902; 12254</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4726; 16793</t>
+          <t>7383; 19530</t>
         </is>
       </c>
     </row>
